--- a/Phase6.2/quantized (Cleaned)/load_49.xlsx
+++ b/Phase6.2/quantized (Cleaned)/load_49.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8720"/>
+    <workbookView windowWidth="18350" windowHeight="8720"/>
   </bookViews>
   <sheets>
     <sheet name="Timestamp logs" sheetId="1" r:id="rId1"/>
@@ -34,14 +34,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,28 +490,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -527,118 +523,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -703,6 +696,9380 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Sensing Unit Program: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$A$1:$A$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>18.3831</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.85</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22.838</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.59</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25.8214</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18.5617</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21.2002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>27.008</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>16.4955</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20.9737</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.051</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21.0747</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>17.3409</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>18.1403</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.5644</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17.5396</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>14.5441</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>23.6824</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>23.3434</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>24.7097</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>17.2321</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>38.5286</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>21.1091</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>16.015</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25.6633</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>21.7024</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28.8412</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>17.6366</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>21.948</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>25.6475</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>26.2632</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>15.8314</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>20.1241</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>23.426</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>128.6271</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>56.8914</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>29.3819</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>17.5089</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>20.6331</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>18.5822</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>17.3268</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>18.553</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>15.8535</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>17.8999</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>24.8243</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>28.181</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>17.4616</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>19.4378</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>28.5953</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>19.6426</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>18.7508</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>121.1591</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>15.4954</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>17.4787</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>14.1289</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>20.1601</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>21.7416</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>19.9394</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>14.0644</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>16.8363</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>13.7907</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>16.7926</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>12.5648</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>14.1387</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>22.7284</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>25.4974</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>27.6662</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>26.2246</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>19.2563</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>41.4321</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>23.8632</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>32.7407</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>19.4257</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>29.3666</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>19.6319</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>21.2203</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>24.5953</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>31.105</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>22.1217</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>32.1932</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>31.166</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>29.0188</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>34.8201</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>37.149</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>23.6656</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>19.575</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>22.4085</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>25.8285</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>29.2789</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>27.8407</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>25.2814</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>23.7625</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>29.8383</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>29.3268</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>27.4889</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>25.1271</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>28.1505</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>26.2235</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>24.6293</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>20.6966</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>20.5064</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>17.6459</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>20.5042</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>33.2576</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>22.4332</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>18.7056</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>31.4572</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>26.9854</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>27.9736</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>35.9475</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>33.1656</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>28.4196</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>33.7115</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>29.5157</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>25.8848</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>17.7303</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>22.6126</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>20.0553</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>18.0464</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>33.0514</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>34.1624</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>16.6862</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>21.8505</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>19.5518</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>25.1247</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>26.2987</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>30.7149</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>33.3084</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>22.4116</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>20.4742</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>19.8101</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>23.624</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>124.718</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>30.6008</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>25.3643</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>23.3422</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>35.6572</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>18.7423</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>25.9176</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>19.106</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>23.1398</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>27.0683</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>21.0076</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>119.9882</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>19.9005</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>33.2928</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>26.1503</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>18.8435</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>17.0172</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>22.5093</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>22.7898</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>22.0049</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>28.6113</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>19.6472</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>25.0132</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>24.1497</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>18.923</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>19.2585</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>17.6109</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>22.0117</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>20.4948</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>22.0145</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>19.403</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>28.3773</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>37.6117</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>22.5495</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>34.3028</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>22.6172</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>20.355</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>17.7371</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>17.9069</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>18.3866</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>18.6505</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>32.3713</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>24.2506</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>32.2293</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>35.5141</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>28.6595</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>19.8847</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>16.4063</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>27.3099</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>24.6576</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>35.5403</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>15.9106</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>21.4173</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>18.396</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>22.7468</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>18.5023</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>21.7625</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>20.2042</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>23.8385</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>21.8236</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>18.7448</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>20.0479</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>19.7872</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>22.1987</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>16.8802</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>21.6752</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>17.1322</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>25.873</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>18.0067</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>19.8761</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>16.549</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>28.8414</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>22.6913</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>18.6108</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>18.121</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>20.8487</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>27.0648</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>44.79</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>56.66</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>43.046</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>28.8964</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>46.9873</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>90.4863</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>27.103</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>28.2605</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>36.2139</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>35.4019</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>27.0731</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>37.3706</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>22.7578</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>30.2308</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>32.3271</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>18.6191</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>12.1382</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>17.2395</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>23.6753</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>15.042</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>23.8277</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>29.3876</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>22.6708</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>33.0008</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>12.0051</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>27.7886</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>20.8159</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>17.5778</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>17.2197</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>17.4331</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>10.1633</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>16.4376</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>20.1833</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>15.9507</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>33.2922</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>118.0191</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>12.2531</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>22.4064</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>18.1842</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>21.7425</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>14.6554</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>23.3177</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>11.8678</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>24.941</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>11.5424</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>15.9586</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>21.765</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>19.188</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>19.8089</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>11.1805</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>18.8993</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>12.3312</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>19.7507</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>12.5998</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>18.7057</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>24.3268</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>24.3748</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>24.4724</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>13.2971</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>29.2356</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>15.4686</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>17.3097</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>12.4601</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>13.3461</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>22.0186</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>32.7226</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>12.3815</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>23.0898</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>14.7585</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>12.6252</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>16.4053</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>24.5376</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>30.7728</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>29.0471</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>12.6123</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>18.7626</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>10.9761</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>10.4514</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>16.5936</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>18.6676</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>11.5537</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>10.2762</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>16.7109</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>10.8207</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>11.7319</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>18.2495</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>24.4823</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>10.3791</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>25.9023</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>20.9267</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>21.0534</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>16.0746</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>22.0751</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>21.0311</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>11.4628</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>22.5336</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>16.2191</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>22.1753</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>22.8893</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>35.7485</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>34.0748</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>27.0222</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>20.8642</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>124.285</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>35.3871</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>20.7094</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>15.8132</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>20.8667</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>15.0573</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>36.0947</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>59.7426</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>32.0234</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>22.1841</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>16.3429</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>15.1199</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>44.3804</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>13.1935</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>27.7488</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>154.6813</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>53.9393</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>45.2741</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>16.0065</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>35.9709</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>18.3914</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>19.3371</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>21.9913</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>58.3303</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>14.0308</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>62.4734</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>18.1723</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>59.598</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>29.092</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>21.8431</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>11.8908</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>29.9433</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>17.6546</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>13.781</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>33.599</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>33.6395</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>17.0033</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>17.6116</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>31.8075</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>30.2872</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>14.3273</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>18.7129</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>16.9658</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>24.5208</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>33.3295</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>30.273</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>79.7533</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>127.2313</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>22.9029</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>20.5681</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>25.7001</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>28.6812</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>14.9538</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>24.5181</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>22.6275</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>21.7297</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>25.4317</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>15.3249</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>11.6957</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>14.6419</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>12.2698</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>11.4902</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>26.0595</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>24.4672</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>19.7029</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>11.3242</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>21.1192</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>20.4499</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>20.6138</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>23.1368</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>11.6131</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>22.6807</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>14.9348</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>11.5941</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>25.0119</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>10.5901</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>19.8449</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>23.7375</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>15.1912</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>11.8869</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>15.1722</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>10.5732</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>24.0957</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>26.6337</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>11.7118</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>20.4006</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>10.1364</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>10.8046</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>14.7875</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>22.2213</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>10.0433</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>11.5145</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>19.6103</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>12.2171</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>29.7172</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>13.4602</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>11.6403</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>11.5247</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>24.8217</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>11.4419</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>18.296</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>17.5456</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>11.7537</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>21.2055</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>27.6778</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>45.0727</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>15.1371</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>20.2031</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>11.0119</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>15.0932</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>24.7738</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>12.1048</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>12.1028</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>16.3401</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>15.6678</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>19.3397</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>11.7607</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>33.207</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>12.8721</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>28.101</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>28.5041</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>12.0082</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>11.0514</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>10.4971</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>17.0016</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>23.0189</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>10.236</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>13.0741</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>17.0829</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>10.2357</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>21.1851</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>38.0071</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>12.7574</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>12.7331</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>14.4322</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>24.2442</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>10.602</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>10.1648</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>11.8806</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>11.3529</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>21.7734</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>16.8678</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>13.7352</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>29.0612</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>11.2279</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>18.242</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>11.5506</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>15.9379</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>13.3097</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>11.6685</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>25.1109</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>14.4685</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>17.9445</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>11.9841</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>19.2096</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>11.7764</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>11.9959</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>15.8304</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>38.9515</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>19.4574</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>24.9045</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>17.725</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>15.0721</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>12.4897</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>19.1773</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>20.9181</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>10.8172</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>19.876</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>13.6804</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>20.5648</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>17.3896</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>25.5786</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>11.6865</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>32.1223</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>14.4913</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>25.5296</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>10.9475</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>11.7118</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>22.5689</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>39.3309</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>10.0447</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>11.4432</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>12.0746</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>15.8766</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="150968462"/>
+        <c:axId val="917950704"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="150968462"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="917950704"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="917950704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="150968462"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Queue Lifetime: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$B$1:$B$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>0.124371</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.164123</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>317.186533</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>265.827567</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>198.429529</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>326.590488</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>360.189801</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>497.97653</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>731.445717</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>666.945161</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>653.280258</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>873.640267</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>868.710688</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1131.561091</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1095.892981</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1293.37476</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1200.047388</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1227.940252</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1442.270577</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1429.647415</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1562.67848</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1520.595912</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1738.98716</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1841.886427</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1843.466339</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1944.197144</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1867.876338</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2195.736156</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2347.377507</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2434.484977</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2515.324895</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2435.836032</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2872.540021</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2912.977299</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3056.312138</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2933.784752</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3029.424941</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3189.922751</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3336.667636</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3484.491136</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3525.97064</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3650.758282</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3750.791469</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3870.654123</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3939.236632</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>4009.347193</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4150.878042</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4211.693657</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4638.284011</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4542.084751</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>4764.498428</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>4718.212309</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>4764.977266</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>4902.656418</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>4922.701192</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5031.57299</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5039.198739</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5257.232404</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5295.347563</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5436.478944</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5399.378811</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5433.299626</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5512.676735</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5531.114054</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5585.592476</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>5657.427921</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5371.595486</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5371.419535</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5668.876251</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5757.48694</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5671.036838</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>5414.648821</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5346.747733</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5513.366305</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5383.671742</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5559.456789</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5277.577875</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5473.009232</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5287.326225</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5268.540729</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5452.288213</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>5328.686868</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5318.966131</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5034.265125</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>5086.648984</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5184.383945</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5152.516034</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5051.777485</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5086.661001</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5239.479407</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5251.413705</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>5041.452123</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>4778.511035</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>4786.906135</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>4830.251005</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>4870.844604</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>4992.205844</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>4886.148461</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4730.157658</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>4957.509487</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5038.16449</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5076.57412</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>4973.803883</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5028.516451</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5008.977875</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5201.396322</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>5281.509479</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5076.410399</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>5073.01379</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5045.391293</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>4893.815098</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>5032.832277</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>5009.864008</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>5025.221323</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>5130.947706</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5302.926972</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>5064.217448</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>5005.513423</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>5065.088726</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>5127.965199</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>5162.392136</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>4922.321162</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>4921.212643</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>5092.719259</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>5205.23501</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>5191.805973</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>5283.537474</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>5391.620364</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>5461.733639</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>5452.325328</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>5509.951582</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>5426.669565</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>5648.14479</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>5529.924699</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>5530.14553</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>5397.196481</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>5587.849691</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>5680.768155</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>6100.268133</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>5958.659587</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>5716.172821</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>5726.956027</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>6173.844574</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>5933.233487</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>5720.732116</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>5925.664417</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>6028.697877</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>5856.291211</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>5855.639805</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>5819.970997</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>5755.29603</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>5802.65018</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>5840.908098</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>5840.505043</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>5773.4423</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>5664.287922</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>5746.071174</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>5709.041168</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>5655.404914</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>5609.139812</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>5735.536401</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>5928.698909</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>5957.610719</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>6074.998427</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>6113.834575</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>6022.867883</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>6085.825527</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>5933.644155</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>5988.647</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>6224.178722</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>6113.564111</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>6410.176082</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>6462.615809</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>6465.912188</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>6601.011263</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>6267.812572</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>6351.737615</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>6414.984131</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>6489.560974</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>6280.339287</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>6138.545285</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>6151.14656</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>6355.887463</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>6677.69112</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>6311.759903</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>6303.867384</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>6310.515023</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>6155.446187</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>6599.200479</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>6532.171028</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>6622.801028</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>6571.843957</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>6565.328532</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>6651.039555</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>6589.332201</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>6650.132931</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>6590.119011</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>6721.356777</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>6609.950703</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>6576.870561</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>6652.165017</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>6824.657349</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>6623.48863</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>6333.307793</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>6331.528973</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>6320.50534</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>6108.625221</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>6193.002916</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>6112.646393</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>6068.440327</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>5878.696881</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>5542.138319</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>5672.543506</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>5405.496554</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>5452.502797</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>5444.619217</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>5286.125374</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>5188.426542</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>5052.766856</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>5122.441185</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>5116.083983</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>5089.358767</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>4996.477738</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>4983.119362</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>4893.845935</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>4656.704445</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>4538.046755</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>4779.654659</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>4693.144111</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>4872.050961</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>4298.257309</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>4185.585392</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>4405.854664</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>4367.349487</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>4209.934378</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>4172.414646</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>4119.573836</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>4256.248988</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>4005.304237</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>3894.342461</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>3848.461857</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>4111.73598</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>4019.230028</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>3904.061447</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>4004.87567</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>3892.389933</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>4024.266489</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>3903.837625</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>3996.267045</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>4291.017899</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>4066.756385</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>4181.869803</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>4062.232962</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>4285.352207</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>4040.359072</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>4036.529729</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>4083.616375</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>3940.511857</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>3954.538606</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>4040.931505</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>4043.282948</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>3921.244494</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>3848.194965</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>3956.630963</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>3890.050846</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>3845.373614</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>3981.135275</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>4162.146725</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>4053.01321</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>4152.192218</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>4134.448366</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>3986.000106</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>4237.383475</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>4275.12788</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>4218.836673</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>4277.967221</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>4465.011794</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>4489.622293</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>4362.727049</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>4372.523608</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>4506.346242</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>4351.025539</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>4340.541867</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>4298.875232</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>4605.402459</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>4631.74335</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>4429.70381</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>4546.798864</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>4649.296879</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>4698.309238</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>4994.773051</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>4707.022362</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>4717.166525</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>4783.780799</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>4835.232908</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>4657.701864</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>4625.459368</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>4779.648157</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>5093.051349</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>5120.453905</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>5053.467404</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>4966.248501</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>5207.470324</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>5208.317087</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>5320.781584</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>5278.793399</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>5279.603478</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>5253.031687</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>5209.676199</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>5107.760336</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>5231.676103</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>5093.857763</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>5244.195905</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>4997.95193</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>4890.150846</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>5102.078864</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>5090.022563</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>5081.202848</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>5182.496431</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>4887.977731</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>5003.239223</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>5131.193411</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>4912.485674</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>4887.290877</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>5108.918245</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>5095.097478</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>5055.18372</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>5080.588195</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>4588.739131</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>4517.292177</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>4428.493328</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>4503.119445</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>4439.821721</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>4511.945014</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>4519.966472</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>4388.306849</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>4489.063848</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>4457.606513</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>4496.791207</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>4498.49628</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>4446.270015</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>4407.158246</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>4375.991581</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>4273.538555</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>4188.34685</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>4009.420294</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>4281.312652</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>4369.352872</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>4345.627075</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>4344.93984</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>4318.506927</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>4200.535684</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>4084.028218</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>4059.603207</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>3960.899282</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>3884.367487</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>3918.256376</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>3991.402511</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>4002.420665</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>3927.796842</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>3815.933977</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>3752.234221</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>3662.382973</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>3711.967914</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>3782.778172</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>3817.274927</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>3778.862277</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>4030.830632</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>3853.783662</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>3857.499413</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>3990.915788</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>4036.438083</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>4098.865458</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>3936.575846</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>3948.945318</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>3723.018885</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>3828.663947</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>3836.151884</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>3684.68491</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>3714.891899</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>3802.306062</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>3574.716169</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>3798.64532</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>3820.492332</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>3724.313139</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>3682.109075</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>3663.27068</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>3693.739024</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>3728.313968</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>3627.52469</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>3589.634765</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>3580.826771</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>3546.106091</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>3586.739199</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>3632.707688</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>3711.443324</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>3595.048441</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>3618.658964</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>3646.726571</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>3567.048196</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>3779.130589</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>3781.84022</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>3676.615154</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>3648.507311</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>3548.445527</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>3524.278289</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>3617.089515</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>3833.950226</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>3809.465591</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>3565.196072</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>3596.726466</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>3677.527816</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>3544.521345</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>3687.07403</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>3702.768373</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>3671.597175</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>3775.220995</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>3862.818367</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>3901.137993</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>3961.525331</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>3942.659779</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>3954.552598</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>3635.590948</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>3733.047122</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>3697.658982</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>3725.504551</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>3789.592961</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>3736.396649</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>3738.956774</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>3731.712723</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>3825.005555</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>3846.266961</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>3839.574066</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>3876.520962</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>4132.127695</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>4057.408503</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>4054.192407</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>3949.148782</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>4007.037015</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>4047.231114</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>4060.174052</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>4192.200216</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>3936.971615</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>3934.940214</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>3909.245392</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>4031.508979</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>4222.7359</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>4287.065107</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>4290.429798</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>4146.501235</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>4073.102234</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>4045.569702</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>4071.342027</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>4057.474346</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>4268.084366</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>4320.001487</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>4366.311076</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>4315.511175</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>4283.316241</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>4247.514175</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>4106.482049</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>4370.00988</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>4343.479102</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>4427.693304</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>4548.586926</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>4527.138011</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>4726.164384</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>4656.892162</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>4748.652227</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>4752.581814</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>4700.020519</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>4765.171402</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>4687.81952</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>4652.205241</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>4784.074591</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>4747.939502</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>4648.121278</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>4917.71959</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>4697.033344</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>4747.03805</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>4776.873374</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>4665.001634</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>4689.021302</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>4852.124134</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>4947.99559</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>4830.279099</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>4965.471727</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>4923.018554</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>4912.243307</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>4807.814478</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>4838.044251</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>5045.707245</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>5115.59823</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>5089.843896</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>5107.109215</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>5088.107567</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>5043.501773</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="691469393"/>
+        <c:axId val="176914532"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="691469393"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="176914532"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="176914532"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="691469393"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Inference Program: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$C$1:$C$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>298.106623</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>483.208252</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>305.438116</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>551.934547</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>597.201187</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>697.350185</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>388.180165</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>492.75989</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>499.820017</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>698.058723</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>506.518723</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>499.310857</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>403.599558</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>448.547001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>449.92844</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>311.469005</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>703.445055</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>394.638999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>499.55882</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>602.019945</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>403.267468</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>495.992879</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>600.180939</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>752.539217</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>608.746946</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>607.460506</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>700.317526</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>796.108186</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>686.36908</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>701.628648</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>803.022043</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>694.950809</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>592.996376</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>609.564355</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>654.932892</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>899.65193</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>596.357708</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>807.2403</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>503.003486</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>655.651088</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>399.014047</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>699.523003</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>496.401787</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>804.455929</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>915.145571</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>647.262342</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>697.87791</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>702.877274</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>405.35619</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>597.235506</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>501.117443</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>497.616148</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>599.751695</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>505.873949</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>602.858552</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>411.037927</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>496.949597</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>903.519972</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>301.234311</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>405.448324</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>498.498085</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>504.958559</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>403.702495</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>606.14745</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>643.005897</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>659.366281</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>599.131249</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>695.708581</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>591.212953</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>448.156842</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>588.849953</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>603.537271</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>797.43108</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>501.875634</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>594.825279</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>900.062576</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>687.92592</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>545.242533</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>396.095785</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>402.536894</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>499.31809</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>325.80613</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>504.280097</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>350.280202</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>896.868037</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>602.77316</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>448.095322</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>495.094808</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>401.478852</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>397.778729</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>308.80234</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>698.479392</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>601.52062</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>608.087859</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>894.250814</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>590.679784</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>604.112928</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>605.913889</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1396.900033</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>698.587151</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>701.075371</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>391.067744</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>795.079239</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>991.855012</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>397.61131</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>398.536745</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>13783.495654</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>508.084043</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>13698.058169</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>789.702307</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>904.462516</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>750.029208</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>590.305298</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>603.197039</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>550.046226</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>704.217006</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>593.705017</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>403.920666</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>406.079834</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>1001.296388</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>800.353489</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>554.065255</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>988.999213</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>1051.19884</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>752.312623</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>499.443935</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>794.095706</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>394.539917</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>989.228809</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>701.584342</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>652.080901</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>602.585377</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>698.047172</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>897.66265</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>794.924046</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>805.707341</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>603.468186</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>1006.284298</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>550.952147</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>991.210976</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>600.036924</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>791.454279</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>599.164598</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>760.527951</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>492.863739</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>596.560485</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>798.200853</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>497.664424</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>398.898753</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>795.624152</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>507.950157</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>848.019058</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>408.900546</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>701.427971</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>650.976782</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>304.303004</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>1191.462894</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>1015.928504</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>607.102594</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>704.313712</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>1105.783941</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>478.241319</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>691.497097</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>1196.992185</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>700.69447</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>1101.42411</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>1254.209662</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>1106.18718</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>801.151284</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1201.79386</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>847.158578</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>701.75112</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>495.936621</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>1110.13284</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>530.777779</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>493.351124</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>584.86441</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>1107.302644</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>501.298778</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>997.401102</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>797.792012</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>798.565029</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>550.098061</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>984.077215</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1099.520954</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>713.488853</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>591.914623</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>898.772198</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>645.638815</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>490.140851</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>1108.454654</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>986.641308</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>318.948461</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>393.734923</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>497.499582</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>701.957031</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>800.255227</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>792.414161</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>706.678101</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>786.594082</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>625.526428</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>616.761429</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>870.086428</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>592.56607</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>854.688175</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>400.434071</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>1048.442282</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>907.627641</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>501.01033</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>703.396561</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>704.963642</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>398.736647</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>543.165633</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>703.294627</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>605.434231</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>900.599712</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>602.681743</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>591.79872</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>503.500414</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>544.416158</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>599.753176</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>597.143041</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>603.525315</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>604.80366</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>898.734624</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>599.555464</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>790.026531</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>623.108586</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>595.801453</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>353.402483</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>691.631661</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>599.994292</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>806.938215</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>853.825079</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>500.53435</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>405.525158</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>777.364719</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>1012.977365</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>700.299877</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>695.010331</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>781.394443</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>949.504742</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>899.015317</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>527.181122</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>892.968088</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>797.829112</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>816.190597</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>1192.669098</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>694.543046</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>1145.028407</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>502.672165</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>402.501218</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>398.680922</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>500.751912</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>494.504034</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>390.14768</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>502.324618</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>542.881182</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>294.466433</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>1000.547158</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>902.009934</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>518.055428</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>1097.320872</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>502.142799</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>554.959613</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>706.561594</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>1002.251055</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>906.782886</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>699.28852</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>946.786812</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>941.879276</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>979.208431</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>1185.516603</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>606.786383</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>693.036532</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>688.870281</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>1048.835501</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>654.597646</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>1322.082622</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>785.776657</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>809.343168</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>601.127114</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>1405.508073</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>795.254438</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>1000.812631</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>1115.492299</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>1253.913029</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>890.76929</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>846.937092</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>796.330916</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>1092.856368</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>564.749699</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>878.66686</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>811.876805</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>1229.212411</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>1205.028395</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>810.651815</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>782.473553</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>712.129972</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>779.49962</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>905.488784</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>585.284202</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>645.866322</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>841.302698</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>1217.904786</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>908.151547</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>499.819113</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>774.309761</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>882.56946</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>859.314547</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>397.383833</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>787.799499</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>1003.337425</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>598.819897</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>1000.064538</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>992.262661</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>501.27178</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>645.353654</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>705.809894</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>888.43151</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>800.246348</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>502.333955</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>523.331334</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>547.622967</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>800.273394</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>641.696907</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>685.188677</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>603.700289</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>869.968717</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>302.715879</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>789.589673</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>552.739782</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>949.866349</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>792.198986</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>844.423963</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>904.952431</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>494.697042</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>696.411047</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>393.039042</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>910.602286</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>699.714505</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>1045.27609</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>502.232106</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>546.119744</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>668.385945</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>491.568184</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>694.208946</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>451.782174</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>608.881276</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>502.508089</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>714.664864</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>915.760193</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>646.506686</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>499.639445</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>597.895623</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>301.705512</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>594.68688</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>698.142789</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>479.459259</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>397.115092</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>803.574646</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>1136.232176</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>694.243296</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>899.112297</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>548.769526</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>808.070021</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>505.469695</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>474.928933</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>439.662948</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>598.939263</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>491.070966</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>375.532506</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>399.63598</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>853.365151</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>894.987515</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>498.751838</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>848.848024</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>677.662392</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>302.345595</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>1001.397845</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>401.635045</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>500.75739</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>503.756669</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>895.567816</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>699.651201</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>589.684257</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>401.618729</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>346.166606</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>601.165794</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>694.719375</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>696.222267</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>550.942193</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>407.890248</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>894.446639</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>710.646362</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>593.368509</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>593.526139</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>451.796502</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>636.128785</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>447.889807</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>591.401964</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>900.054696</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>684.414555</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>896.96832</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>597.391211</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>553.639631</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>897.81077</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>607.975062</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>599.29397</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>704.929455</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>1014.72515</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>598.55893</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>798.472565</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>697.636354</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>444.755323</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>598.109854</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>404.956864</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>900.578862</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>548.042677</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>602.86897</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>402.053621</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>404.301327</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>452.770646</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>1001.655111</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>696.684096</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>622.78491</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>502.169923</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>992.565751</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>1031.61158</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>797.235332</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>648.442873</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>791.410579</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>797.719495</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>600.522845</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>699.905388</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>949.667013</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>1063.327513</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>397.555006</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>493.950673</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>900.851864</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>402.111029</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>845.72762</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>895.766838</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>694.622458</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>346.778377</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>797.561529</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>449.516282</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>1143.040216</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>1276.125354</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>603.119999</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>745.528369</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>811.34763</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>952.018855</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>652.727889</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>816.59492</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>604.983262</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>896.414912</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>833.942253</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>1214.049136</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>1283.939421</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>513.989275</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>839.906245</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>902.280268</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>838.758335</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>802.001312</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>1069.620315</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>685.530374</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>855.164919</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>785.892963</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>1104.531927</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>540.400643</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>884.687458</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>760.009555</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>725.241204</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>698.341247</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>508.364661</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>983.475145</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>702.530744</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>1213.185273</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>803.256498</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>756.540651</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>1000.636131</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>302.462477</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>599.398185</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>1205.180646</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>894.360085</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>1372.107828</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>802.877289</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>584.940024</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>1000.423128</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>478.043946</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>1001.042003</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>794.994231</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>890.600119</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>556.570352</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>795.239172</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>600.230488</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="176432591"/>
+        <c:axId val="980237815"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="176432591"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="980237815"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="980237815"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="176432591"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Entire Pipeline: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$D$1:$D$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>316.614094</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>501.222375</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>645.462649</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>837.352114</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>821.452116</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1042.502373</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>769.570166</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1012.63642</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1258.273734</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1381.499384</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1180.772681</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1393.002124</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1293.384946</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1597.448992</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1563.961721</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1624.408165</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1921.032043</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1637.123351</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1965.511797</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2055.01076</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1990.655648</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2033.820891</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2377.696699</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2615.534744</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2468.228285</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2577.32095</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2589.896264</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3020.685542</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3051.383187</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3158.061625</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3343.994438</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3157.050041</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3481.367797</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3542.665754</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3734.67103</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3962.063782</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3682.674049</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>4026.544951</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3857.180022</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4160.775324</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3943.566887</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>4367.608085</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4265.746256</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>4690.963552</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>4872.282103</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>4681.433835</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4876.936952</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4932.032531</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>5063.078001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>5167.915557</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5285.258471</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5234.579257</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5485.888061</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>5424.025767</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5543.038444</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5456.739817</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5556.308436</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>6182.493976</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5616.521274</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5855.991668</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5914.713196</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5952.048885</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5933.17183</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>6149.826304</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>6242.737073</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>6339.522602</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5996.224135</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>6094.794316</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>6286.313804</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>6224.900082</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>6301.318891</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>6042.049292</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>6176.919513</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>6034.667639</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>6007.863621</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>6479.151265</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5986.724095</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>6042.847065</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5714.52701</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5693.199323</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5983.799503</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>5685.658998</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5852.265028</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>5419.365427</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>6020.666021</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5810.822705</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5620.186356</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5569.280793</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5513.968353</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5666.537036</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5588.056745</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>5765.212915</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>5403.794155</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>5424.832294</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5753.828619</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5489.013288</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5621.445872</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5520.21285</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>6153.281191</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5680.725938</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5759.936461</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5488.148264</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>5786.529022</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>6040.875663</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5439.846785</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5622.366267</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>19083.710733</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5615.951642</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>18798.057359</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5863.0672</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5834.225114</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>5816.027085</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>5628.588906</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>5662.129862</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>5710.509632</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>6033.028778</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>5675.652765</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>5432.046689</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>5491.22386</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>6147.307987</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>5995.797025</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>5510.548817</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>5926.898056</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>6165.768599</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>5977.099433</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>5716.374608</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>6103.93188</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>5816.875181</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>6484.270848</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>6176.32127</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>6182.506683</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>6049.065042</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>6369.815962</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>6552.305349</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>6355.670376</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>6228.268122</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>6214.660077</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>6722.709653</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>6669.96258</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>6975.788163</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>6335.315745</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>6541.550106</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>6800.077472</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>6714.769038</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>6333.584055</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>6542.125402</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>6860.19153</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>6380.105935</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>6273.382058</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>6632.612349</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>6285.755487</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>6673.459038</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>6271.813544</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>6570.544314</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>6444.066282</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>5993.604126</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>6961.683768</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>6743.892672</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>6281.766008</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>6331.064424</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>6863.332042</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>6427.435028</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>6671.122316</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>7291.393612</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>6842.906345</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>7161.903693</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>7362.584689</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>7074.134135</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>6812.415484</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>7446.327582</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>6978.459789</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>7129.834102</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>6976.93903</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>7594.695528</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>7164.160342</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>6785.414296</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>6968.831325</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>7557.800875</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>7019.519252</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>7297.625089</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>6952.743597</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>6977.021489</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>6930.643124</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>7697.308635</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>7427.191457</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>7038.773537</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>6920.825646</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>7076.965185</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>7263.341594</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>7044.074379</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>7751.459882</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>7582.323765</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>6906.100593</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>7063.519278</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>7106.879683</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>7371.877162</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>7412.572938</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>7530.651138</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>7338.304004</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>7380.596843</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>7303.564445</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>7459.425478</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>7513.451158</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>6942.422863</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>7215.058548</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>6743.630711</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>7175.678303</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>7118.751557</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>6634.505423</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>6798.901688</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>6628.450523</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>5997.534966</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>6258.755139</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>6137.687581</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>6104.924328</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>6435.705229</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>5915.910117</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>5808.485762</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>5592.48117</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>5702.259243</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>5742.910259</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>5723.872408</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>5622.760853</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>5618.153822</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>5824.907659</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>5274.879009</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>5340.211486</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>5420.002745</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>5312.620864</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>5240.495444</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>5013.71667</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>4814.967284</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>5235.463679</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>5254.175366</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>4722.473828</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>4605.728404</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>4917.754455</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>5286.804153</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>4722.823814</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>4606.785892</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>4640.0196</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>5077.678322</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>4938.428645</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>4447.193269</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>4931.135958</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>4808.238145</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>4852.710186</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>5118.913123</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>4708.994291</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>5457.788806</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>4584.08395</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>4607.688721</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>4472.781684</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>4811.045119</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>4546.405506</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>4442.636009</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>4607.705993</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>4502.581039</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>4268.813939</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>5052.659163</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>4964.192182</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>4451.631122</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>4965.266537</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>4471.373562</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>4463.716159</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>4576.262008</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>5007.76113</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>5093.402011</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>4765.59883</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>5128.21463</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>5091.796242</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>4982.518237</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>5435.360178</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>4895.260363</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>4933.891805</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>4999.560102</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>5526.228795</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>5167.309739</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>5699.568171</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>5170.925465</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>5332.09471</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>4976.690253</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>5776.82274</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>5123.17677</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>5618.82739</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>5765.998249</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>5694.592939</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>5448.019554</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>5512.827571</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>5513.307754</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>6099.183119</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>5282.048261</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>5612.544285</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>5606.478304</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>6076.177219</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>5880.979759</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>5460.593483</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>5572.50081</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>5831.083621</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>5920.880225</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>5980.009588</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>5567.607303</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>5875.411746</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>6070.650885</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>6550.14917</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>6209.478546</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>5795.641691</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>6049.516748</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>6115.134959</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>6002.823383</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>5663.134736</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>5908.679462</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>6268.39753</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>5721.056827</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>5925.602484</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>6115.050925</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>5607.107543</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>5747.423202</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>5903.363625</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>5812.503941</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>5863.228171</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>5665.550766</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>5458.001108</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>5451.256744</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>5924.311539</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>5781.174785</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>5753.565897</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>5712.037284</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>5613.389148</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>4873.947356</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>5263.357101</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>5071.865727</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>5425.65897</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>5322.5354</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>5383.727535</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>5315.25058</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>5042.09119</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>5168.04836</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>4952.303649</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>5427.270866</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>5205.58252</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>5481.526336</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>4900.066787</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>4831.549099</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>4886.676095</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>4518.643078</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>4989.302598</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>4854.734046</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>4988.147851</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>4864.451229</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>5050.783391</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>5148.103377</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>4760.822104</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>4573.569952</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>4577.507805</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>4203.038799</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>4537.464056</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>4722.8748</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>4512.152924</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>4404.665234</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>4746.739923</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>4911.369297</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>4377.194369</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>4636.780311</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>4360.228898</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>4640.298748</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>4308.850072</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>4528.387065</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>4315.17631</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>4481.870376</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>4497.311654</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>4423.666289</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>4513.143338</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>4802.210797</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>4855.423033</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>4247.830223</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>4701.979171</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>4533.517176</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>3998.354705</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>4737.408944</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>4224.391007</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>4096.087359</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>4325.538789</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>4727.673248</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>4446.64504</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>4286.728132</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>4076.483509</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>4064.91753</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>4340.069862</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>4342.088965</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>4309.594532</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>4146.960164</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>3965.883239</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>4496.358038</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>4353.92725</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>4328.907533</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>4215.20828</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>4082.167266</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>4303.255956</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>4025.074403</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>4381.337153</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>4696.682416</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>4383.251009</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>4555.518931</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>4157.351238</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>4097.52822</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>4527.117385</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>4471.642488</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>4422.219761</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>4281.765827</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>4622.976316</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>4300.908446</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>4354.43581</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>4403.006384</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>4165.069296</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>4281.460729</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>4201.383359</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>4791.075029</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>4494.25337</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>4579.531401</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>4364.9165</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>4369.865825</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>4103.454794</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>4759.476033</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>4406.447878</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>4360.392261</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>4308.102984</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>4744.6302</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>4789.908054</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>4540.708755</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>4506.655428</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>4650.54964</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>4665.394561</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>4505.547907</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>4844.041283</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>5018.126916</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>5128.01702</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>4363.705388</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>4524.006588</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>4958.318978</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>4475.359181</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>5055.010736</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>4842.974153</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>4650.747772</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>4294.030869</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>4841.827908</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>4684.985282</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>5444.537523</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>5590.799352</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>4760.223234</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>4828.795403</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>4868.797932</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>5034.713782</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>4731.975635</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>5101.547086</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>4938.719949</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>5291.787188</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>5160.681328</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>5515.607377</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>5543.004196</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>4636.409224</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>5223.225825</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>5257.42787</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>5291.562539</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>5365.056738</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>5614.702826</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>5423.678858</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>5531.266681</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>5546.32159</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>5869.109641</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>5256.251562</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>5688.81036</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>5467.286475</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>5402.350945</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>5500.140838</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>5271.376263</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>5644.086123</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>5639.427634</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>5931.136717</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>5561.111748</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>5553.290025</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>5679.318165</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>5012.048579</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>5468.911919</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>6178.754836</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>5736.325684</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>6369.701855</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>5740.387143</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>5522.712931</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>5819.185106</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>5327.799997</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>6069.318148</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>5949.923361</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>5990.488715</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>5675.122767</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>5895.421339</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>5659.608861</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="649534877"/>
+        <c:axId val="894397174"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="649534877"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="894397174"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="894397174"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="649534877"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="2500"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>876300</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>158750</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3333750" y="69850"/>
+        <a:ext cx="7721600" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>107950</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3460750" y="2940050"/>
+        <a:ext cx="7588250" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>107950</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3460750" y="5810250"/>
+        <a:ext cx="7588250" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>158115</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3517900" y="8731250"/>
+        <a:ext cx="7536815" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8455,5 +17822,6 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>